--- a/data/trans_orig/P36B02_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36B02_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>451674</t>
+          <t>453121</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>474604</t>
+          <t>474453</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>425205</t>
+          <t>425023</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>445830</t>
+          <t>445124</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>884097</t>
+          <t>886342</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>913258</t>
+          <t>914486</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19460</t>
+          <t>19611</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42390</t>
+          <t>40943</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21659</t>
+          <t>22365</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42284</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48295</t>
+          <t>47067</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77456</t>
+          <t>75211</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>678547</t>
+          <t>677346</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>704228</t>
+          <t>703952</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>577352</t>
+          <t>576749</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>600773</t>
+          <t>601160</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1262770</t>
+          <t>1265624</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1298799</t>
+          <t>1299376</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30379</t>
+          <t>30655</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56060</t>
+          <t>57261</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24721</t>
+          <t>24334</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48142</t>
+          <t>48745</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61302</t>
+          <t>60725</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>97331</t>
+          <t>94477</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>570667</t>
+          <t>569051</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>599329</t>
+          <t>597490</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>636918</t>
+          <t>636588</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>660799</t>
+          <t>662676</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1213965</t>
+          <t>1214843</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1252031</t>
+          <t>1253532</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39339</t>
+          <t>41178</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68001</t>
+          <t>69617</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27813</t>
+          <t>25936</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51694</t>
+          <t>52024</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75248</t>
+          <t>73747</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113314</t>
+          <t>112436</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>459216</t>
+          <t>458352</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>487242</t>
+          <t>487724</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>473931</t>
+          <t>474404</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>494721</t>
+          <t>495514</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>943332</t>
+          <t>942049</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>976778</t>
+          <t>977895</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31905</t>
+          <t>31423</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59931</t>
+          <t>60795</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20921</t>
+          <t>20128</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41711</t>
+          <t>41238</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58011</t>
+          <t>56894</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>91457</t>
+          <t>92740</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>344518</t>
+          <t>344242</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>364916</t>
+          <t>365149</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>359418</t>
+          <t>361209</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>381845</t>
+          <t>382754</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>712117</t>
+          <t>713874</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>744123</t>
+          <t>742863</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21794</t>
+          <t>21561</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42192</t>
+          <t>42468</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22141</t>
+          <t>21232</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44568</t>
+          <t>42777</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46573</t>
+          <t>47833</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78579</t>
+          <t>76822</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>258921</t>
+          <t>258211</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>277308</t>
+          <t>276814</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>315936</t>
+          <t>316728</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>332161</t>
+          <t>332546</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>582696</t>
+          <t>582985</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>606942</t>
+          <t>606565</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15275</t>
+          <t>15769</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33662</t>
+          <t>34372</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>10388</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26998</t>
+          <t>26206</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28575</t>
+          <t>28952</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>52821</t>
+          <t>52532</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>191557</t>
+          <t>191992</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>204791</t>
+          <t>204647</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>315720</t>
+          <t>314933</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>329329</t>
+          <t>328370</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>513038</t>
+          <t>512621</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>531328</t>
+          <t>530868</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18326</t>
+          <t>17891</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18188</t>
+          <t>18975</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12463</t>
+          <t>12923</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>30753</t>
+          <t>31170</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3010865</t>
+          <t>3011724</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3070960</t>
+          <t>3071974</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3157344</t>
+          <t>3159450</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3209454</t>
+          <t>3214503</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6182195</t>
+          <t>6188622</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6267216</t>
+          <t>6266671</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>204701</t>
+          <t>203687</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>264796</t>
+          <t>263937</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>168611</t>
+          <t>163562</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>220721</t>
+          <t>218615</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>386510</t>
+          <t>387055</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>471531</t>
+          <t>465104</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>419314</t>
+          <t>418380</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>437471</t>
+          <t>436912</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>385646</t>
+          <t>385265</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>407281</t>
+          <t>406951</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>809624</t>
+          <t>811472</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>839560</t>
+          <t>839611</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15762</t>
+          <t>16321</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33919</t>
+          <t>34853</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22949</t>
+          <t>23279</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44584</t>
+          <t>44965</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43903</t>
+          <t>43852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73839</t>
+          <t>71991</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>623502</t>
+          <t>621148</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>651432</t>
+          <t>649824</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>544867</t>
+          <t>544187</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>572890</t>
+          <t>573054</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1177694</t>
+          <t>1178275</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1216049</t>
+          <t>1215870</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35655</t>
+          <t>37263</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63585</t>
+          <t>65939</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37365</t>
+          <t>37201</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65388</t>
+          <t>66068</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>81293</t>
+          <t>81472</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119648</t>
+          <t>119067</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>622785</t>
+          <t>621745</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>650720</t>
+          <t>650776</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>650708</t>
+          <t>651091</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>676889</t>
+          <t>677977</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1282211</t>
+          <t>1283816</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1320585</t>
+          <t>1321440</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,08%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31143</t>
+          <t>31087</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59078</t>
+          <t>60118</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31090</t>
+          <t>30002</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57271</t>
+          <t>56888</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>69257</t>
+          <t>68402</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>107631</t>
+          <t>106026</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>552505</t>
+          <t>551153</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>580772</t>
+          <t>579950</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>562373</t>
+          <t>561894</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>588337</t>
+          <t>588917</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1123355</t>
+          <t>1124210</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1162076</t>
+          <t>1163440</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33845</t>
+          <t>34667</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62112</t>
+          <t>63464</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26839</t>
+          <t>26259</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52803</t>
+          <t>53282</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67716</t>
+          <t>66352</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>106437</t>
+          <t>105582</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>375462</t>
+          <t>375368</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>401389</t>
+          <t>401387</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>417825</t>
+          <t>417363</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>435284</t>
+          <t>435778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>801611</t>
+          <t>802052</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>832051</t>
+          <t>833162</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28040</t>
+          <t>28042</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53967</t>
+          <t>54061</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11471</t>
+          <t>10977</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28930</t>
+          <t>29392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44134</t>
+          <t>43023</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74574</t>
+          <t>74133</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>286882</t>
+          <t>287142</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>303021</t>
+          <t>302842</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>336200</t>
+          <t>335645</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>348981</t>
+          <t>348266</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>629500</t>
+          <t>628420</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>648988</t>
+          <t>648788</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22904</t>
+          <t>22644</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16810</t>
+          <t>17365</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13809</t>
+          <t>14009</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33297</t>
+          <t>34377</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>225094</t>
+          <t>225217</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>242438</t>
+          <t>242420</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>362669</t>
+          <t>363490</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>379867</t>
+          <t>380102</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>596537</t>
+          <t>596985</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>619247</t>
+          <t>619163</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7413</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24757</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26310</t>
+          <t>25489</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19583</t>
+          <t>19667</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>42293</t>
+          <t>41845</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3161665</t>
+          <t>3165996</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3227948</t>
+          <t>3224637</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3313344</t>
+          <t>3314081</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3374125</t>
+          <t>3372541</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6498776</t>
+          <t>6501487</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6586109</t>
+          <t>6583665</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>197917</t>
+          <t>201228</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>264200</t>
+          <t>259869</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>178260</t>
+          <t>179844</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>239041</t>
+          <t>238304</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>392141</t>
+          <t>394585</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>479474</t>
+          <t>476763</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>385606</t>
+          <t>384056</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>404117</t>
+          <t>403775</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>350678</t>
+          <t>351147</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>371616</t>
+          <t>371932</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>742588</t>
+          <t>743258</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>770797</t>
+          <t>770669</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13317</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31828</t>
+          <t>33378</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24139</t>
+          <t>23823</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45077</t>
+          <t>44608</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42392</t>
+          <t>42520</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70601</t>
+          <t>69931</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>509725</t>
+          <t>509994</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>540591</t>
+          <t>541709</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>517074</t>
+          <t>516365</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>538370</t>
+          <t>538441</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1036949</t>
+          <t>1036802</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1073849</t>
+          <t>1073518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48985</t>
+          <t>47867</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79851</t>
+          <t>79582</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25174</t>
+          <t>25103</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46470</t>
+          <t>47179</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79270</t>
+          <t>79601</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>116170</t>
+          <t>116317</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>586982</t>
+          <t>586461</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>618834</t>
+          <t>617952</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>609195</t>
+          <t>609224</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>632732</t>
+          <t>631645</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1207028</t>
+          <t>1203761</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1246496</t>
+          <t>1243894</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48286</t>
+          <t>49168</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80138</t>
+          <t>80659</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27773</t>
+          <t>28860</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51310</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81130</t>
+          <t>83732</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120598</t>
+          <t>123865</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>561569</t>
+          <t>560591</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>593409</t>
+          <t>592768</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>586516</t>
+          <t>585087</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>612592</t>
+          <t>613573</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1155993</t>
+          <t>1157480</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1198228</t>
+          <t>1197246</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51556</t>
+          <t>52197</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>83396</t>
+          <t>84374</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34399</t>
+          <t>33418</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60475</t>
+          <t>61904</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93728</t>
+          <t>94710</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135963</t>
+          <t>134476</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>424699</t>
+          <t>425163</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>450368</t>
+          <t>450431</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>453136</t>
+          <t>453224</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>476440</t>
+          <t>477062</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>887862</t>
+          <t>887197</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>924484</t>
+          <t>922227</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,61%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27550</t>
+          <t>27487</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53219</t>
+          <t>52755</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20409</t>
+          <t>19787</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43713</t>
+          <t>43625</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50283</t>
+          <t>52540</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86905</t>
+          <t>87570</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>313598</t>
+          <t>312853</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>327501</t>
+          <t>326564</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>347331</t>
+          <t>348481</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>365500</t>
+          <t>365486</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>667349</t>
+          <t>666963</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>688879</t>
+          <t>689020</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>7766</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20732</t>
+          <t>21477</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12262</t>
+          <t>12276</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30431</t>
+          <t>29281</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23213</t>
+          <t>23072</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44743</t>
+          <t>45129</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>233243</t>
+          <t>233069</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>246818</t>
+          <t>247288</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>384067</t>
+          <t>383132</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>397708</t>
+          <t>396686</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>624241</t>
+          <t>623217</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>641567</t>
+          <t>641942</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9288</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22863</t>
+          <t>23037</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>17037</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14708</t>
+          <t>14333</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32034</t>
+          <t>33058</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3074831</t>
+          <t>3074343</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3142986</t>
+          <t>3139692</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3301378</t>
+          <t>3301831</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3359736</t>
+          <t>3356938</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6397489</t>
+          <t>6394732</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6478012</t>
+          <t>6479156</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>244462</t>
+          <t>247756</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>312617</t>
+          <t>313105</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>181839</t>
+          <t>184637</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>240197</t>
+          <t>239744</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>451011</t>
+          <t>449867</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>531534</t>
+          <t>534291</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>351463</t>
+          <t>350929</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>327119</t>
+          <t>325260</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>369264</t>
+          <t>372911</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>286003</t>
+          <t>328872</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>271034</t>
+          <t>310258</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>296802</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>637467</t>
+          <t>679802</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>608701</t>
+          <t>649252</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>661637</t>
+          <t>702473</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>91,19%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48524</t>
+          <t>56864</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30723</t>
+          <t>34882</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72868</t>
+          <t>82533</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27197</t>
+          <t>33640</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16398</t>
+          <t>20807</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42166</t>
+          <t>52254</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>75720</t>
+          <t>90503</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51550</t>
+          <t>67832</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104486</t>
+          <t>121053</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>365470</t>
+          <t>414650</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>345256</t>
+          <t>395312</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>380741</t>
+          <t>433535</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>392106</t>
+          <t>446725</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>232147</t>
+          <t>430423</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>459335</t>
+          <t>459765</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>757576</t>
+          <t>861374</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>571495</t>
+          <t>834741</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>826077</t>
+          <t>883261</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>90,32%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>58077</t>
+          <t>62240</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42806</t>
+          <t>43355</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78291</t>
+          <t>81578</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>119398</t>
+          <t>54358</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52169</t>
+          <t>41318</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>279357</t>
+          <t>70660</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>177475</t>
+          <t>116599</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>108974</t>
+          <t>94712</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>363556</t>
+          <t>143232</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>469390</t>
+          <t>544470</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>450421</t>
+          <t>524385</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>485013</t>
+          <t>561121</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>476115</t>
+          <t>544130</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>462657</t>
+          <t>527657</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>487483</t>
+          <t>557081</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>945505</t>
+          <t>1088600</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>922777</t>
+          <t>1065711</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>965940</t>
+          <t>1110818</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,37%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>66948</t>
+          <t>76367</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51325</t>
+          <t>59716</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85917</t>
+          <t>96452</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>66353</t>
+          <t>78009</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54985</t>
+          <t>65058</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79811</t>
+          <t>94482</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>133301</t>
+          <t>154376</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112866</t>
+          <t>132158</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>156029</t>
+          <t>177265</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>804954</t>
+          <t>611976</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>764179</t>
+          <t>591881</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>849743</t>
+          <t>629163</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>638797</t>
+          <t>655814</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>624152</t>
+          <t>642832</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>652444</t>
+          <t>668935</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1443752</t>
+          <t>1267790</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1405474</t>
+          <t>1245149</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1499583</t>
+          <t>1288868</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>89,68%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>82832</t>
+          <t>88641</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38043</t>
+          <t>71454</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>123607</t>
+          <t>108736</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>73701</t>
+          <t>80681</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60054</t>
+          <t>67560</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>88346</t>
+          <t>93663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>156533</t>
+          <t>169322</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>100702</t>
+          <t>148244</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>194811</t>
+          <t>191963</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>476684</t>
+          <t>520101</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>460494</t>
+          <t>501948</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>492952</t>
+          <t>535882</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>478366</t>
+          <t>531027</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>465055</t>
+          <t>517481</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>489341</t>
+          <t>542589</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>955050</t>
+          <t>1051128</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>932493</t>
+          <t>1027224</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>973037</t>
+          <t>1071014</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,92%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>84550</t>
+          <t>89245</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>73464</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>100740</t>
+          <t>107398</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>69539</t>
+          <t>77828</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58564</t>
+          <t>66266</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82850</t>
+          <t>91374</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>154089</t>
+          <t>167074</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>136102</t>
+          <t>147188</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>176646</t>
+          <t>190978</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>325944</t>
+          <t>359323</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>314375</t>
+          <t>347132</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>334778</t>
+          <t>369111</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>569497</t>
+          <t>394889</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>544631</t>
+          <t>385140</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>591987</t>
+          <t>402790</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>895441</t>
+          <t>754212</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>867759</t>
+          <t>737412</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>933070</t>
+          <t>768331</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>90,79%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>42221</t>
+          <t>47757</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33387</t>
+          <t>37969</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53790</t>
+          <t>59948</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>38871</t>
+          <t>44277</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16381</t>
+          <t>36376</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63737</t>
+          <t>54026</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>81092</t>
+          <t>92034</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43463</t>
+          <t>77915</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>108774</t>
+          <t>108834</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>253567</t>
+          <t>278086</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>244884</t>
+          <t>268001</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>261578</t>
+          <t>285832</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>387801</t>
+          <t>421225</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>377991</t>
+          <t>411156</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>395385</t>
+          <t>431323</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>641368</t>
+          <t>699311</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>628264</t>
+          <t>684377</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>652455</t>
+          <t>711211</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,79%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>29192</t>
+          <t>32112</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21181</t>
+          <t>24366</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37875</t>
+          <t>42197</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>38030</t>
+          <t>43384</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30446</t>
+          <t>33286</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47840</t>
+          <t>53453</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>67222</t>
+          <t>75496</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>56135</t>
+          <t>63596</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>80326</t>
+          <t>90430</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3047473</t>
+          <t>3079536</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2989897</t>
+          <t>3032838</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3136156</t>
+          <t>3124665</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3228685</t>
+          <t>3322683</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3024967</t>
+          <t>3286012</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3314975</t>
+          <t>3355599</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>6276158</t>
+          <t>6402219</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6055024</t>
+          <t>6349366</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6388820</t>
+          <t>6455660</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>88,83%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>412344</t>
+          <t>453226</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>323661</t>
+          <t>408097</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>469920</t>
+          <t>499924</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>433089</t>
+          <t>412177</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>346799</t>
+          <t>379261</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>636807</t>
+          <t>448848</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>845433</t>
+          <t>865403</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>732771</t>
+          <t>811962</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1066567</t>
+          <t>918256</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3661774</t>
+          <t>3734860</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3661774</t>
+          <t>3734860</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3661774</t>
+          <t>3734860</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7121591</t>
+          <t>7267622</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7121591</t>
+          <t>7267622</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7121591</t>
+          <t>7267622</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
